--- a/grupos/4ARHM - Estadisticos 20232.xlsx
+++ b/grupos/4ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -233,15 +233,15 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -257,49 +257,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>OREA</t>
+  </si>
+  <si>
     <t>PALMA</t>
   </si>
   <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>ESPARZA</t>
@@ -308,79 +308,52 @@
     <t>RANGEL</t>
   </si>
   <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
   </si>
   <si>
     <t>DIEGO ANTONIO</t>
   </si>
   <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
     <t>ANGELES VALERIA</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
     <t>FATIMA</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
   </si>
   <si>
     <t>EDUARDO</t>
   </si>
   <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
     <t>JESUS ALEJANDRO</t>
   </si>
   <si>
     <t>KEVIN RAUL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -888,22 +861,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -924,19 +897,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>7</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -965,22 +938,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1001,22 +974,22 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1042,22 +1015,22 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1084,13 +1057,13 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1119,22 +1092,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1161,16 +1134,16 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1196,22 +1169,22 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1235,13 +1208,13 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1273,22 +1246,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1318,13 +1291,13 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1350,22 +1323,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1389,7 +1362,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1398,7 +1371,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1427,22 +1400,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1466,16 +1439,16 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1504,22 +1477,22 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1540,22 +1513,22 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1581,22 +1554,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1617,22 +1590,22 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>6</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1658,22 +1631,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1735,22 +1708,22 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1771,22 +1744,22 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>7</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1812,22 +1785,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1848,10 +1821,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1860,10 +1833,10 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1889,22 +1862,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1966,22 +1939,22 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2002,22 +1975,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>5</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>5</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2043,22 +2016,22 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2082,16 +2055,16 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>10</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2120,22 +2093,22 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2156,22 +2129,22 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>5</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2197,22 +2170,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2239,16 +2212,16 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2274,22 +2247,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2313,16 +2286,16 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2351,22 +2324,22 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2387,16 +2360,16 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2428,22 +2401,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2467,7 +2440,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2476,10 +2449,10 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2505,22 +2478,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2547,13 +2520,13 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2582,22 +2555,22 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2618,13 +2591,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>5</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2633,7 +2606,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2659,22 +2632,22 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2695,22 +2668,22 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2736,22 +2709,22 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2772,22 +2745,22 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2813,22 +2786,22 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2855,13 +2828,13 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>7</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2890,22 +2863,22 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2926,19 +2899,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -2967,22 +2940,22 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3009,13 +2982,13 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>6</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3044,22 +3017,22 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3086,16 +3059,16 @@
         <v>5</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3121,22 +3094,22 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3157,13 +3130,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3198,22 +3171,22 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3246,10 +3219,10 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3275,22 +3248,22 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3323,10 +3296,10 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3352,22 +3325,22 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3391,16 +3364,16 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>10</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3429,22 +3402,22 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3477,10 +3450,10 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3506,22 +3479,22 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3542,16 +3515,16 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>7</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -3583,22 +3556,22 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3631,7 +3604,7 @@
         <v>10</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3660,22 +3633,22 @@
         <v>6</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3696,7 +3669,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>5</v>
@@ -3705,10 +3678,10 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>6</v>
@@ -3737,22 +3710,22 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3776,10 +3749,10 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -3788,7 +3761,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3814,22 +3787,22 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3850,7 +3823,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -3859,7 +3832,7 @@
         <v>5</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X42">
         <v>5</v>
@@ -3891,22 +3864,22 @@
         <v>10</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3968,22 +3941,22 @@
         <v>7</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4004,7 +3977,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U44">
         <v>6</v>
@@ -4016,7 +3989,7 @@
         <v>8</v>
       </c>
       <c r="X44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y44">
         <v>7</v>
@@ -4045,22 +4018,22 @@
         <v>8</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4084,16 +4057,16 @@
         <v>10</v>
       </c>
       <c r="U45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y45">
         <v>8</v>
@@ -4122,22 +4095,22 @@
         <v>6</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4158,10 +4131,10 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V46">
         <v>10</v>
@@ -4170,7 +4143,7 @@
         <v>7</v>
       </c>
       <c r="X46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y46">
         <v>6</v>
@@ -4199,22 +4172,22 @@
         <v>10</v>
       </c>
       <c r="H47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N47">
         <v>-1</v>
@@ -4238,10 +4211,10 @@
         <v>10</v>
       </c>
       <c r="U47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W47">
         <v>10</v>
@@ -4276,22 +4249,22 @@
         <v>6</v>
       </c>
       <c r="H48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N48">
         <v>-1</v>
@@ -4318,16 +4291,16 @@
         <v>5</v>
       </c>
       <c r="V48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y48">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4466,7 +4439,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -4484,7 +4457,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4525,14 +4498,14 @@
         <v>100</v>
       </c>
       <c r="I5">
+        <v>97.5</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
         <v>95</v>
       </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
       <c r="L5">
         <v>100</v>
       </c>
@@ -4543,13 +4516,13 @@
         <v>100</v>
       </c>
       <c r="O5">
+        <v>97.5</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
         <v>95</v>
-      </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
-      <c r="Q5">
-        <v>100</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4643,13 +4616,13 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4661,13 +4634,13 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4761,7 +4734,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -4779,7 +4752,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -5003,13 +4976,13 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -5021,13 +4994,13 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -5115,13 +5088,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -5133,13 +5106,13 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -5174,13 +5147,13 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -5192,13 +5165,13 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -5292,10 +5265,10 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="J18">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -5304,16 +5277,16 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>18.8</v>
+        <v>46.9</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="P18">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5322,7 +5295,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>18.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -5351,13 +5324,13 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5369,13 +5342,13 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5410,16 +5383,16 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -5428,16 +5401,16 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5475,7 +5448,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5493,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5587,13 +5560,13 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5605,13 +5578,13 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5646,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -5664,7 +5637,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5764,7 +5737,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -5776,13 +5749,13 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5794,7 +5767,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5829,7 +5802,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5847,7 +5820,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5944,16 +5917,16 @@
         <v>75</v>
       </c>
       <c r="J29">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K29">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -5962,16 +5935,16 @@
         <v>75</v>
       </c>
       <c r="P29">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q29">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -6000,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -6018,7 +5991,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6056,40 +6029,40 @@
         <v>37.5</v>
       </c>
       <c r="H31">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I31">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J31">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="K31">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M31">
-        <v>37.5</v>
+        <v>46.9</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O31">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="P31">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="Q31">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="S31">
-        <v>37.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -6118,13 +6091,13 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -6136,13 +6109,13 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -6177,10 +6150,10 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J33">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="K33">
         <v>96</v>
@@ -6195,10 +6168,10 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P33">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q33">
         <v>96</v>
@@ -6236,13 +6209,13 @@
         <v>100</v>
       </c>
       <c r="I34">
+        <v>92.5</v>
+      </c>
+      <c r="J34">
         <v>90</v>
       </c>
-      <c r="J34">
-        <v>80</v>
-      </c>
       <c r="K34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -6254,13 +6227,13 @@
         <v>100</v>
       </c>
       <c r="O34">
+        <v>92.5</v>
+      </c>
+      <c r="P34">
         <v>90</v>
       </c>
-      <c r="P34">
-        <v>80</v>
-      </c>
       <c r="Q34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -6295,37 +6268,37 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J35">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
-        <v>37.5</v>
+        <v>56.3</v>
       </c>
       <c r="N35">
         <v>100</v>
       </c>
       <c r="O35">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="P35">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>37.5</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6472,7 +6445,7 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J38">
         <v>100</v>
@@ -6490,7 +6463,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -6590,13 +6563,13 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="J40">
         <v>100</v>
       </c>
       <c r="K40">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L40">
         <v>100</v>
@@ -6608,13 +6581,13 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -6705,40 +6678,40 @@
         <v>37.5</v>
       </c>
       <c r="H42">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I42">
-        <v>55</v>
+        <v>72.5</v>
       </c>
       <c r="J42">
         <v>100</v>
       </c>
       <c r="K42">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L42">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M42">
-        <v>37.5</v>
+        <v>40.6</v>
       </c>
       <c r="N42">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O42">
-        <v>55</v>
+        <v>72.5</v>
       </c>
       <c r="P42">
         <v>100</v>
       </c>
       <c r="Q42">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="R42">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S42">
-        <v>37.5</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6944,13 +6917,13 @@
         <v>100</v>
       </c>
       <c r="I46">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J46">
         <v>100</v>
       </c>
       <c r="K46">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L46">
         <v>100</v>
@@ -6962,13 +6935,13 @@
         <v>100</v>
       </c>
       <c r="O46">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P46">
         <v>100</v>
       </c>
       <c r="Q46">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R46">
         <v>100</v>
@@ -7062,16 +7035,16 @@
         <v>100</v>
       </c>
       <c r="I48">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J48">
         <v>100</v>
       </c>
       <c r="K48">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L48">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M48">
         <v>100</v>
@@ -7080,16 +7053,16 @@
         <v>100</v>
       </c>
       <c r="O48">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P48">
         <v>100</v>
       </c>
       <c r="Q48">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R48">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S48">
         <v>100</v>
@@ -7158,19 +7131,19 @@
         <v>45</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>55.6</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>44.4</v>
+        <v>31.1</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7190,19 +7163,19 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>91.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="G3" s="2">
-        <v>8.9</v>
+        <v>22.2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7213,7 +7186,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
@@ -7222,19 +7195,19 @@
         <v>45</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="G4" s="2">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7245,7 +7218,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
@@ -7254,19 +7227,19 @@
         <v>45</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>93.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7277,7 +7250,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
@@ -7298,7 +7271,7 @@
         <v>4.4</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7318,19 +7291,19 @@
         <v>45</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>97.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7380,7 +7353,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7412,16 +7385,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920237</v>
+        <v>22330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7435,22 +7408,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920237</v>
+        <v>22330051920212</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7458,16 +7431,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920218</v>
+        <v>22330051920064</v>
       </c>
       <c r="B4" t="s">
         <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7481,22 +7454,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920218</v>
+        <v>22330051920064</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7504,16 +7477,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920242</v>
+        <v>21330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -7527,22 +7500,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920242</v>
+        <v>21330051920237</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7550,22 +7523,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920333</v>
+        <v>22330051920068</v>
       </c>
       <c r="B8" t="s">
         <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7573,22 +7546,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920054</v>
+        <v>22330051920068</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7596,16 +7569,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920058</v>
+        <v>22330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -7619,22 +7592,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920062</v>
+        <v>22330051920218</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7642,16 +7615,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920423</v>
+        <v>21330051920053</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -7665,22 +7638,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920064</v>
+        <v>21330051920053</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7688,16 +7661,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920334</v>
+        <v>21330051920242</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -7711,22 +7684,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920359</v>
+        <v>21330051920242</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7734,16 +7707,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920068</v>
+        <v>22330051920054</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7757,22 +7730,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920317</v>
+        <v>22330051920059</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7780,22 +7753,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920425</v>
+        <v>22330051920061</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7803,16 +7776,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920083</v>
+        <v>21330051920359</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -7826,16 +7799,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920084</v>
+        <v>22330051920317</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -7844,6 +7817,29 @@
         <v>69</v>
       </c>
       <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920425</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20232.xlsx
+++ b/grupos/4ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -230,21 +230,21 @@
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Hernández Castro Enrique</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -257,100 +257,85 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
   </si>
   <si>
     <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
   </si>
   <si>
     <t>KEVIN RAUL</t>
@@ -879,22 +864,22 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -903,16 +888,16 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -956,22 +941,22 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -980,16 +965,16 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1033,40 +1018,40 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>7</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>7</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1110,22 +1095,22 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1134,16 +1119,16 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1187,22 +1172,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1264,25 +1249,25 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1341,22 +1326,22 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1368,13 +1353,13 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1418,28 +1403,28 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1448,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1495,28 +1480,28 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1572,31 +1557,31 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>8</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1605,7 +1590,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1649,22 +1634,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1726,31 +1711,31 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1759,7 +1744,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1803,28 +1788,28 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1833,7 +1818,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1880,22 +1865,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1957,22 +1942,22 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -1984,13 +1969,13 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2034,22 +2019,22 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2067,7 +2052,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2111,40 +2096,40 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>7</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2188,22 +2173,22 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2212,10 +2197,10 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2265,22 +2250,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2295,7 +2280,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2342,34 +2327,34 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2419,22 +2404,22 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2443,13 +2428,13 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2496,22 +2481,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2520,13 +2505,13 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2573,22 +2558,22 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>6</v>
@@ -2600,13 +2585,13 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2650,40 +2635,40 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>6</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2727,22 +2712,22 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2757,7 +2742,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2804,22 +2789,22 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -2828,7 +2813,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -2881,22 +2866,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2905,13 +2890,13 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -2958,37 +2943,37 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>5</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3035,31 +3020,31 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>5</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -3068,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3112,31 +3097,31 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3189,22 +3174,22 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3213,7 +3198,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3222,7 +3207,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3266,22 +3251,22 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3293,13 +3278,13 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3343,22 +3328,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3367,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3420,22 +3405,22 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3497,34 +3482,34 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>8</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -3574,22 +3559,22 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3604,7 +3589,7 @@
         <v>10</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3651,22 +3636,22 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
         <v>8</v>
@@ -3678,7 +3663,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>8</v>
@@ -3728,22 +3713,22 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -3758,10 +3743,10 @@
         <v>8</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3805,25 +3790,25 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -3835,7 +3820,7 @@
         <v>5</v>
       </c>
       <c r="X42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y42">
         <v>5</v>
@@ -3882,22 +3867,22 @@
         <v>10</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
         <v>10</v>
@@ -3959,40 +3944,40 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
         <v>9</v>
       </c>
       <c r="U44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V44">
         <v>10</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X44">
         <v>9</v>
       </c>
       <c r="Y44">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4036,22 +4021,22 @@
         <v>8</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T45">
         <v>10</v>
@@ -4066,7 +4051,7 @@
         <v>8</v>
       </c>
       <c r="X45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y45">
         <v>8</v>
@@ -4113,40 +4098,40 @@
         <v>6</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T46">
         <v>10</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V46">
         <v>10</v>
       </c>
       <c r="W46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X46">
         <v>8</v>
       </c>
       <c r="Y46">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -4190,22 +4175,22 @@
         <v>10</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T47">
         <v>10</v>
@@ -4220,7 +4205,7 @@
         <v>10</v>
       </c>
       <c r="X47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y47">
         <v>10</v>
@@ -4267,40 +4252,40 @@
         <v>5</v>
       </c>
       <c r="N48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P48">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U48">
         <v>5</v>
       </c>
       <c r="V48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W48">
         <v>6</v>
       </c>
       <c r="X48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y48">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4457,7 +4442,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4516,13 +4501,13 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4581,7 +4566,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -4634,13 +4619,13 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4752,7 +4737,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4988,19 +4973,19 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q13">
-        <v>93</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -5106,13 +5091,13 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -5165,13 +5150,13 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -5283,10 +5268,10 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P18">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5295,7 +5280,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>46.9</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -5342,13 +5327,13 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5401,16 +5386,16 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q20">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R20">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5460,13 +5445,13 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5578,13 +5563,13 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5637,7 +5622,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5755,19 +5740,19 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>87.5</v>
+        <v>54.7</v>
       </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>84.40000000000001</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5814,13 +5799,13 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P27">
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5932,19 +5917,19 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="P29">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q29">
-        <v>93</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>68.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5991,7 +5976,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6047,22 +6032,22 @@
         <v>46.9</v>
       </c>
       <c r="N31">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="O31">
-        <v>75</v>
+        <v>82.8</v>
       </c>
       <c r="P31">
-        <v>72.5</v>
+        <v>82.8</v>
       </c>
       <c r="Q31">
-        <v>91</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="R31">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S31">
-        <v>46.9</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -6109,13 +6094,13 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q32">
-        <v>93</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -6168,13 +6153,13 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P33">
-        <v>70</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q33">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -6227,13 +6212,13 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>92.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P34">
-        <v>90</v>
+        <v>79.7</v>
       </c>
       <c r="Q34">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -6286,19 +6271,19 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="P35">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q35">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>56.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6345,10 +6330,10 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6463,7 +6448,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38">
         <v>100</v>
@@ -6581,13 +6566,13 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>87.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P40">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q40">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -6696,22 +6681,22 @@
         <v>40.6</v>
       </c>
       <c r="N42">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="O42">
-        <v>72.5</v>
+        <v>70.3</v>
       </c>
       <c r="P42">
-        <v>100</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q42">
-        <v>93</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="R42">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S42">
-        <v>40.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6935,13 +6920,13 @@
         <v>100</v>
       </c>
       <c r="O46">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P46">
         <v>100</v>
       </c>
       <c r="Q46">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R46">
         <v>100</v>
@@ -7053,16 +7038,16 @@
         <v>100</v>
       </c>
       <c r="O48">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P48">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q48">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R48">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S48">
         <v>100</v>
@@ -7154,7 +7139,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
@@ -7163,19 +7148,19 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>77.8</v>
+        <v>82.2</v>
       </c>
       <c r="G3" s="2">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7186,7 +7171,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
@@ -7207,7 +7192,7 @@
         <v>13.3</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7218,7 +7203,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
@@ -7227,19 +7212,19 @@
         <v>45</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="G5" s="2">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7250,7 +7235,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
@@ -7259,19 +7244,19 @@
         <v>45</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7282,7 +7267,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>74</v>
@@ -7291,19 +7276,19 @@
         <v>45</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7353,7 +7338,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7385,16 +7370,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920212</v>
+        <v>22330051920333</v>
       </c>
       <c r="B2" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7408,22 +7393,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920212</v>
+        <v>22330051920333</v>
       </c>
       <c r="B3" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7431,16 +7416,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920064</v>
+        <v>22330051920054</v>
       </c>
       <c r="B4" t="s">
         <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7454,22 +7439,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920064</v>
+        <v>22330051920054</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7477,16 +7462,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920237</v>
+        <v>22330051920212</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -7500,22 +7485,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920237</v>
+        <v>22330051920212</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7523,22 +7508,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920068</v>
+        <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
         <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7546,22 +7531,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920068</v>
+        <v>22330051920071</v>
       </c>
       <c r="B9" t="s">
         <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7569,16 +7554,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920218</v>
+        <v>22330051920317</v>
       </c>
       <c r="B10" t="s">
         <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -7592,19 +7577,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920218</v>
+        <v>22330051920317</v>
       </c>
       <c r="B11" t="s">
         <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
         <v>70</v>
@@ -7615,16 +7600,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920053</v>
+        <v>22330051920084</v>
       </c>
       <c r="B12" t="s">
         <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -7638,19 +7623,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920053</v>
+        <v>22330051920084</v>
       </c>
       <c r="B13" t="s">
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>70</v>
@@ -7661,16 +7646,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920242</v>
+        <v>22330051920059</v>
       </c>
       <c r="B14" t="s">
         <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -7684,22 +7669,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920242</v>
+        <v>21330051920359</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7707,16 +7692,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920054</v>
+        <v>22330051920218</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7730,116 +7715,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920059</v>
+        <v>22330051920425</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920061</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920359</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920317</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920425</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21">
         <v>5</v>
       </c>
     </row>
